--- a/data/reports/report-2026-08-18.xlsx
+++ b/data/reports/report-2026-08-18.xlsx
@@ -724,13 +724,13 @@
         <v>2.19</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>421995</v>
+        <v>421977</v>
       </c>
       <c r="H6" s="5" t="n">
-        <v>188585</v>
+        <v>188567</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>39016</v>
+        <v>38998</v>
       </c>
       <c r="J6" s="6" t="n">
         <v>0.996</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>+25%（週+29,751円）</t>
+          <t>+25%（週+32,158円）</t>
         </is>
       </c>
     </row>
@@ -818,13 +818,13 @@
         <v>2.63</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>21615</v>
+        <v>21614</v>
       </c>
       <c r="H8" s="5" t="n">
-        <v>14139</v>
+        <v>14138</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>14865</v>
+        <v>14864</v>
       </c>
       <c r="J8" s="6" t="n">
         <v>0.994</v>
@@ -865,13 +865,13 @@
         <v>4.01</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>61742</v>
+        <v>61740</v>
       </c>
       <c r="H9" s="5" t="n">
-        <v>41996</v>
+        <v>41994</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="J9" s="6" t="n">
         <v>0.993</v>
@@ -955,13 +955,13 @@
         <v>3.31</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>-20186</v>
+        <v>-20188</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>-19483</v>
+        <v>-19485</v>
       </c>
       <c r="I11" s="8" t="n">
-        <v>-4126</v>
+        <v>-4128</v>
       </c>
       <c r="J11" s="6" t="n">
         <v>0.989</v>
@@ -1002,13 +1002,13 @@
         <v>4.16</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>46995</v>
+        <v>46985</v>
       </c>
       <c r="H12" s="5" t="n">
-        <v>27680</v>
+        <v>27670</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>9678</v>
+        <v>9668</v>
       </c>
       <c r="J12" s="6" t="n">
         <v>0.887</v>
@@ -1049,13 +1049,13 @@
         <v>2.4</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>39855</v>
+        <v>39828</v>
       </c>
       <c r="H13" s="5" t="n">
-        <v>25520</v>
+        <v>25493</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>6550</v>
+        <v>6523</v>
       </c>
       <c r="J13" s="6" t="n">
         <v>1.001</v>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>−25%（週+1,694円）</t>
+          <t>−25%（週+1,700円）</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
         <v>3.14</v>
       </c>
       <c r="D14" s="4" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="E14" s="4" t="n">
         <v>1.57</v>
@@ -1096,13 +1096,13 @@
         <v>3.51</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>35113</v>
+        <v>35107</v>
       </c>
       <c r="H14" s="5" t="n">
-        <v>26064</v>
+        <v>26058</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>2262</v>
+        <v>2256</v>
       </c>
       <c r="J14" s="6" t="n">
         <v>0.984</v>
@@ -1117,7 +1117,7 @@
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>−25%（週+341円）</t>
+          <t>−25%（週+342円）</t>
         </is>
       </c>
     </row>
@@ -1190,13 +1190,13 @@
         <v>3.01</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>51369</v>
+        <v>51366</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>17644</v>
+        <v>17641</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>-229</v>
+        <v>-232</v>
       </c>
       <c r="J16" s="6" t="n">
         <v>0.989</v>
@@ -1211,7 +1211,7 @@
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>+25%（週+3,844円）</t>
+          <t>+25%（週+3,843円）</t>
         </is>
       </c>
     </row>
@@ -1237,13 +1237,13 @@
         <v>2.68</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>10598</v>
+        <v>10590</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>-13025</v>
+        <v>-13033</v>
       </c>
       <c r="I17" s="8" t="n">
-        <v>-10474</v>
+        <v>-10482</v>
       </c>
       <c r="J17" s="6" t="n">
         <v>1.047</v>
@@ -1258,7 +1258,7 @@
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>−25%（週+4,064円）</t>
+          <t>−25%（週+4,065円）</t>
         </is>
       </c>
     </row>
@@ -1378,13 +1378,13 @@
         <v>3.89</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>-18406</v>
+        <v>-18417</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>-10899</v>
+        <v>-10910</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>-3359</v>
+        <v>-3370</v>
       </c>
       <c r="J20" s="6" t="n">
         <v>0.988</v>
@@ -1425,19 +1425,19 @@
         <v>2.6</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>22551</v>
+        <v>22548</v>
       </c>
       <c r="H21" s="5" t="n">
-        <v>12879</v>
+        <v>12876</v>
       </c>
       <c r="I21" s="5" t="n">
-        <v>6081</v>
+        <v>6078</v>
       </c>
       <c r="J21" s="6" t="n">
         <v>1.008</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>0.148</v>
+        <v>0.147</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>+25%（週+1,291円）</t>
+          <t>+25%（週+1,290円）</t>
         </is>
       </c>
     </row>
@@ -1836,10 +1836,10 @@
         <v>1671180</v>
       </c>
       <c r="I6" s="5" t="n">
-        <v>1693551</v>
+        <v>1693557</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>1218114</v>
+        <v>1218108</v>
       </c>
       <c r="K6" s="6" t="n">
         <v>0.2658</v>
@@ -1851,16 +1851,16 @@
         <v>194469</v>
       </c>
       <c r="N6" s="5" t="n">
-        <v>88426</v>
+        <v>88432</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>35113</v>
+        <v>35107</v>
       </c>
       <c r="P6" s="9" t="n">
         <v>2.2</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>2262</v>
+        <v>2256</v>
       </c>
       <c r="R6" s="5" t="n">
         <v>8850</v>
@@ -1950,10 +1950,10 @@
         <v>965568</v>
       </c>
       <c r="I8" s="5" t="n">
-        <v>2131351</v>
+        <v>2131369</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>1939373</v>
+        <v>1939355</v>
       </c>
       <c r="K8" s="6" t="n">
         <v>0.3851</v>
@@ -1965,16 +1965,16 @@
         <v>1213502</v>
       </c>
       <c r="N8" s="5" t="n">
-        <v>557627</v>
+        <v>557645</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>422003</v>
+        <v>421985</v>
       </c>
       <c r="P8" s="9" t="n">
         <v>2.18</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>38994</v>
+        <v>38976</v>
       </c>
       <c r="R8" s="5" t="n">
         <v>80000</v>
@@ -2008,10 +2008,10 @@
         <v>981750</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>1460163</v>
+        <v>1460164</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>1184772</v>
+        <v>1184771</v>
       </c>
       <c r="K9" s="6" t="n">
         <v>0.3267</v>
@@ -2023,16 +2023,16 @@
         <v>363291</v>
       </c>
       <c r="N9" s="5" t="n">
-        <v>243501</v>
+        <v>243502</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>21615</v>
+        <v>21614</v>
       </c>
       <c r="P9" s="9" t="n">
         <v>1.49</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>14865</v>
+        <v>14864</v>
       </c>
       <c r="R9" s="5" t="n">
         <v>35000</v>
@@ -2066,10 +2066,10 @@
         <v>782964</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>900587</v>
+        <v>900589</v>
       </c>
       <c r="J10" s="5" t="n">
-        <v>450778</v>
+        <v>450776</v>
       </c>
       <c r="K10" s="6" t="n">
         <v>0.2112</v>
@@ -2081,16 +2081,16 @@
         <v>247013</v>
       </c>
       <c r="N10" s="5" t="n">
-        <v>181159</v>
+        <v>181161</v>
       </c>
       <c r="O10" s="8" t="n">
-        <v>-20186</v>
+        <v>-20188</v>
       </c>
       <c r="P10" s="9" t="n">
         <v>1.36</v>
       </c>
       <c r="Q10" s="8" t="n">
-        <v>-4126</v>
+        <v>-4128</v>
       </c>
       <c r="R10" s="5" t="n">
         <v>17250</v>
@@ -2124,10 +2124,10 @@
         <v>500038</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>881473</v>
+        <v>881481</v>
       </c>
       <c r="J11" s="5" t="n">
-        <v>467314</v>
+        <v>467306</v>
       </c>
       <c r="K11" s="6" t="n">
         <v>0.2528</v>
@@ -2139,16 +2139,16 @@
         <v>165834</v>
       </c>
       <c r="N11" s="5" t="n">
-        <v>109421</v>
+        <v>109429</v>
       </c>
       <c r="O11" s="5" t="n">
-        <v>10598</v>
+        <v>10590</v>
       </c>
       <c r="P11" s="9" t="n">
         <v>1.52</v>
       </c>
       <c r="Q11" s="8" t="n">
-        <v>-10474</v>
+        <v>-10482</v>
       </c>
       <c r="R11" s="5" t="n">
         <v>10000</v>
@@ -2182,10 +2182,10 @@
         <v>244682</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>620251</v>
+        <v>620278</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>201309</v>
+        <v>201282</v>
       </c>
       <c r="K12" s="6" t="n">
         <v>0.1888</v>
@@ -2197,16 +2197,16 @@
         <v>202781</v>
       </c>
       <c r="N12" s="5" t="n">
-        <v>115597</v>
+        <v>115624</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>39855</v>
+        <v>39828</v>
       </c>
       <c r="P12" s="9" t="n">
         <v>1.75</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>6550</v>
+        <v>6523</v>
       </c>
       <c r="R12" s="5" t="n">
         <v>16500</v>
@@ -2298,10 +2298,10 @@
         <v>595974</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>499800</v>
+        <v>499802</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>340570</v>
+        <v>340568</v>
       </c>
       <c r="K14" s="6" t="n">
         <v>0.2371</v>
@@ -2313,16 +2313,16 @@
         <v>335040</v>
       </c>
       <c r="N14" s="5" t="n">
-        <v>138994</v>
+        <v>138996</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>61742</v>
+        <v>61740</v>
       </c>
       <c r="P14" s="9" t="n">
         <v>2.41</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="R14" s="5" t="n">
         <v>20000</v>
@@ -2414,10 +2414,10 @@
         <v>500808</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>409155</v>
+        <v>409166</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>360933</v>
+        <v>360922</v>
       </c>
       <c r="K16" s="6" t="n">
         <v>0.284</v>
@@ -2429,16 +2429,16 @@
         <v>84660</v>
       </c>
       <c r="N16" s="5" t="n">
-        <v>69802</v>
+        <v>69813</v>
       </c>
       <c r="O16" s="8" t="n">
-        <v>-18406</v>
+        <v>-18417</v>
       </c>
       <c r="P16" s="9" t="n">
         <v>1.21</v>
       </c>
       <c r="Q16" s="8" t="n">
-        <v>-3359</v>
+        <v>-3370</v>
       </c>
       <c r="R16" s="5" t="inlineStr"/>
     </row>
@@ -2858,10 +2858,10 @@
         <v>82152</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>168477</v>
+        <v>168480</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>53151</v>
+        <v>53148</v>
       </c>
       <c r="K24" s="6" t="n">
         <v>0.175</v>
@@ -2873,16 +2873,16 @@
         <v>78684</v>
       </c>
       <c r="N24" s="5" t="n">
-        <v>35269</v>
+        <v>35272</v>
       </c>
       <c r="O24" s="5" t="n">
-        <v>22551</v>
+        <v>22548</v>
       </c>
       <c r="P24" s="9" t="n">
         <v>2.23</v>
       </c>
       <c r="Q24" s="5" t="n">
-        <v>6081</v>
+        <v>6078</v>
       </c>
       <c r="R24" s="5" t="n">
         <v>5000</v>
@@ -2970,13 +2970,13 @@
         <v>186528</v>
       </c>
       <c r="I26" s="5" t="n">
-        <v>158539</v>
+        <v>158549</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>113591</v>
+        <v>113581</v>
       </c>
       <c r="K26" s="6" t="n">
-        <v>0.2477</v>
+        <v>0.2476</v>
       </c>
       <c r="L26" s="16" t="n">
         <v>2.89</v>
@@ -2985,16 +2985,16 @@
         <v>246510</v>
       </c>
       <c r="N26" s="5" t="n">
-        <v>98479</v>
+        <v>98489</v>
       </c>
       <c r="O26" s="5" t="n">
-        <v>46995</v>
+        <v>46985</v>
       </c>
       <c r="P26" s="9" t="n">
         <v>2.5</v>
       </c>
       <c r="Q26" s="5" t="n">
-        <v>9678</v>
+        <v>9668</v>
       </c>
       <c r="R26" s="5" t="n">
         <v>15000</v>
@@ -3090,10 +3090,10 @@
         <v>103227</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>142877</v>
+        <v>142880</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>85693</v>
+        <v>85690</v>
       </c>
       <c r="K28" s="6" t="n">
         <v>0.2583</v>
@@ -3105,16 +3105,16 @@
         <v>176709</v>
       </c>
       <c r="N28" s="5" t="n">
-        <v>69199</v>
+        <v>69202</v>
       </c>
       <c r="O28" s="5" t="n">
-        <v>51369</v>
+        <v>51366</v>
       </c>
       <c r="P28" s="9" t="n">
         <v>2.55</v>
       </c>
       <c r="Q28" s="8" t="n">
-        <v>-229</v>
+        <v>-232</v>
       </c>
       <c r="R28" s="5" t="n">
         <v>10000</v>
@@ -3288,16 +3288,16 @@
         <v>5190</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>7488</v>
+        <v>7494</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>2262</v>
+        <v>2256</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.1514</v>
+        <v>0.151</v>
       </c>
       <c r="G7" s="9" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H7" s="9" t="n">
         <v>0.42</v>
@@ -3316,13 +3316,13 @@
         <v>29410</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>25949</v>
+        <v>25955</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>26064</v>
+        <v>26058</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.3201</v>
+        <v>0.32</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>3.14</v>
@@ -3344,13 +3344,13 @@
         <v>70930</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>88426</v>
+        <v>88432</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>35113</v>
+        <v>35107</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.1806</v>
+        <v>0.1805</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>2.2</v>
@@ -3372,10 +3372,10 @@
         <v>1671180</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1693551</v>
+        <v>1693557</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1218114</v>
+        <v>1218108</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.2658</v>
@@ -6336,16 +6336,16 @@
         <v>0.3474</v>
       </c>
       <c r="K63" s="22" t="n">
-        <v>7488</v>
+        <v>7494</v>
       </c>
       <c r="L63" s="22" t="n">
-        <v>2262</v>
+        <v>2256</v>
       </c>
       <c r="M63" s="23" t="n">
-        <v>0.1514</v>
+        <v>0.151</v>
       </c>
       <c r="N63" s="16" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="O63" s="21" t="n">
         <v>2.33</v>
@@ -6354,7 +6354,7 @@
         <v>8850</v>
       </c>
       <c r="Q63" s="23" t="n">
-        <v>0.846</v>
+        <v>0.847</v>
       </c>
       <c r="R63" s="24" t="inlineStr"/>
     </row>
@@ -9611,13 +9611,13 @@
         <v>24816</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>65938</v>
+        <v>65956</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>38994</v>
+        <v>38976</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.3005</v>
+        <v>0.3004</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>1.97</v>
@@ -9639,10 +9639,10 @@
         <v>103024</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>245584</v>
+        <v>245602</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>188692</v>
+        <v>188674</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>0.3512</v>
@@ -9667,13 +9667,13 @@
         <v>233872</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>557627</v>
+        <v>557645</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>422003</v>
+        <v>421985</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.3478</v>
+        <v>0.3477</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>2.18</v>
@@ -9695,10 +9695,10 @@
         <v>965568</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>2131351</v>
+        <v>2131369</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1939373</v>
+        <v>1939355</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.3851</v>
@@ -12639,19 +12639,19 @@
         <v>0.1913</v>
       </c>
       <c r="K63" s="22" t="n">
-        <v>65938</v>
+        <v>65956</v>
       </c>
       <c r="L63" s="22" t="n">
-        <v>38994</v>
+        <v>38976</v>
       </c>
       <c r="M63" s="23" t="n">
-        <v>0.3005</v>
+        <v>0.3004</v>
       </c>
       <c r="N63" s="16" t="n">
         <v>1.97</v>
       </c>
       <c r="O63" s="21" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="P63" s="22" t="n">
         <v>80000</v>
@@ -12772,10 +12772,10 @@
         <v>17017</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>28625</v>
+        <v>28626</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>14865</v>
+        <v>14864</v>
       </c>
       <c r="F7" s="6" t="n">
         <v>0.2457</v>
@@ -12800,10 +12800,10 @@
         <v>44506</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>104450</v>
+        <v>104451</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>14139</v>
+        <v>14138</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>0.0867</v>
@@ -12828,10 +12828,10 @@
         <v>98175</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>243501</v>
+        <v>243502</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>21615</v>
+        <v>21614</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>0.0595</v>
@@ -12856,10 +12856,10 @@
         <v>981750</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>1460163</v>
+        <v>1460164</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>1184772</v>
+        <v>1184771</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.3267</v>
@@ -15788,10 +15788,10 @@
         <v>0.2812</v>
       </c>
       <c r="K63" s="22" t="n">
-        <v>28625</v>
+        <v>28626</v>
       </c>
       <c r="L63" s="22" t="n">
-        <v>14865</v>
+        <v>14864</v>
       </c>
       <c r="M63" s="23" t="n">
         <v>0.2457</v>
@@ -15921,13 +15921,13 @@
         <v>8604</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>19402</v>
+        <v>19404</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-4126</v>
+        <v>-4128</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>-0.1728</v>
+        <v>-0.1729</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>1.23</v>
@@ -15949,10 +15949,10 @@
         <v>25812</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>65311</v>
+        <v>65313</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-19483</v>
+        <v>-19485</v>
       </c>
       <c r="F8" s="14" t="n">
         <v>-0.272</v>
@@ -15977,10 +15977,10 @@
         <v>86040</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>181159</v>
+        <v>181161</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-20186</v>
+        <v>-20188</v>
       </c>
       <c r="F9" s="14" t="n">
         <v>-0.08169999999999999</v>
@@ -16005,10 +16005,10 @@
         <v>782964</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>900587</v>
+        <v>900589</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>450778</v>
+        <v>450776</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.2112</v>
@@ -18945,13 +18945,13 @@
         <v>0.3603</v>
       </c>
       <c r="K63" s="22" t="n">
-        <v>19402</v>
+        <v>19404</v>
       </c>
       <c r="L63" s="25" t="n">
-        <v>-4126</v>
+        <v>-4128</v>
       </c>
       <c r="M63" s="26" t="n">
-        <v>-0.1728</v>
+        <v>-0.1729</v>
       </c>
       <c r="N63" s="18" t="n">
         <v>1.23</v>
@@ -19082,10 +19082,10 @@
         <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>10474</v>
+        <v>10482</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-10474</v>
+        <v>-10482</v>
       </c>
       <c r="F7" s="6" t="inlineStr"/>
       <c r="G7" s="9" t="n">
@@ -19108,13 +19108,13 @@
         <v>11781</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>45068</v>
+        <v>45076</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-13025</v>
+        <v>-13033</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>-0.2972</v>
+        <v>-0.2974</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>0.97</v>
@@ -19136,10 +19136,10 @@
         <v>45815</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>109421</v>
+        <v>109429</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>10598</v>
+        <v>10590</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>0.0639</v>
@@ -19164,10 +19164,10 @@
         <v>500038</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>881473</v>
+        <v>881481</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>467314</v>
+        <v>467306</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.2528</v>
@@ -22102,10 +22102,10 @@
       </c>
       <c r="J63" s="23" t="inlineStr"/>
       <c r="K63" s="22" t="n">
-        <v>10474</v>
+        <v>10482</v>
       </c>
       <c r="L63" s="25" t="n">
-        <v>-10474</v>
+        <v>-10482</v>
       </c>
       <c r="M63" s="23" t="inlineStr"/>
       <c r="N63" s="21" t="inlineStr"/>
@@ -22114,7 +22114,7 @@
         <v>10000</v>
       </c>
       <c r="Q63" s="23" t="n">
-        <v>1.047</v>
+        <v>1.048</v>
       </c>
       <c r="R63" s="29" t="inlineStr">
         <is>
@@ -22233,13 +22233,13 @@
         <v>6251</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>13467</v>
+        <v>13494</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>6550</v>
+        <v>6523</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.2494</v>
+        <v>0.2483</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>1.95</v>
@@ -22261,13 +22261,13 @@
         <v>23218</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>50563</v>
+        <v>50590</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>25520</v>
+        <v>25493</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.257</v>
+        <v>0.2567</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>1.96</v>
@@ -22289,13 +22289,13 @@
         <v>47329</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>115597</v>
+        <v>115624</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>39855</v>
+        <v>39828</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>0.1965</v>
+        <v>0.1964</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>1.75</v>
@@ -22317,10 +22317,10 @@
         <v>244682</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>620251</v>
+        <v>620278</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>201309</v>
+        <v>201282</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.1888</v>
@@ -25245,25 +25245,25 @@
         <v>0.238</v>
       </c>
       <c r="K63" s="22" t="n">
-        <v>13467</v>
+        <v>13494</v>
       </c>
       <c r="L63" s="22" t="n">
-        <v>6550</v>
+        <v>6523</v>
       </c>
       <c r="M63" s="23" t="n">
-        <v>0.2494</v>
+        <v>0.2483</v>
       </c>
       <c r="N63" s="16" t="n">
         <v>1.95</v>
       </c>
       <c r="O63" s="21" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="P63" s="22" t="n">
         <v>16500</v>
       </c>
       <c r="Q63" s="23" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="R63" s="24" t="inlineStr"/>
     </row>
@@ -28286,13 +28286,13 @@
         <v>11192</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>16591</v>
+        <v>16593</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.0049</v>
+        <v>0.0048</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>1.68</v>
@@ -28314,10 +28314,10 @@
         <v>69950</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>62554</v>
+        <v>62556</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>41996</v>
+        <v>41994</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>0.2407</v>
@@ -28342,10 +28342,10 @@
         <v>134304</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>138994</v>
+        <v>138996</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>61742</v>
+        <v>61740</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>0.1843</v>
@@ -28370,10 +28370,10 @@
         <v>595974</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>499800</v>
+        <v>499802</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>340570</v>
+        <v>340568</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.2371</v>
@@ -31130,13 +31130,13 @@
         <v>0.4009</v>
       </c>
       <c r="K63" s="22" t="n">
-        <v>16591</v>
+        <v>16593</v>
       </c>
       <c r="L63" s="22" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="M63" s="23" t="n">
-        <v>0.0049</v>
+        <v>0.0048</v>
       </c>
       <c r="N63" s="18" t="n">
         <v>1.68</v>
@@ -34776,10 +34776,10 @@
         <v>0</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>3359</v>
+        <v>3370</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-3359</v>
+        <v>-3370</v>
       </c>
       <c r="F7" s="6" t="inlineStr"/>
       <c r="G7" s="9" t="n">
@@ -34802,13 +34802,13 @@
         <v>5544</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>19299</v>
+        <v>19310</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>-10899</v>
+        <v>-10910</v>
       </c>
       <c r="F8" s="14" t="n">
-        <v>-0.7816</v>
+        <v>-0.7824</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>0.72</v>
@@ -34830,13 +34830,13 @@
         <v>33264</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>69802</v>
+        <v>69813</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>-18406</v>
+        <v>-18417</v>
       </c>
       <c r="F9" s="14" t="n">
-        <v>-0.2174</v>
+        <v>-0.2175</v>
       </c>
       <c r="G9" s="9" t="n">
         <v>1.21</v>
@@ -34858,10 +34858,10 @@
         <v>500808</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>409155</v>
+        <v>409166</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>360933</v>
+        <v>360922</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.284</v>
@@ -37556,10 +37556,10 @@
       </c>
       <c r="J63" s="23" t="inlineStr"/>
       <c r="K63" s="22" t="n">
-        <v>3359</v>
+        <v>3370</v>
       </c>
       <c r="L63" s="25" t="n">
-        <v>-3359</v>
+        <v>-3370</v>
       </c>
       <c r="M63" s="23" t="inlineStr"/>
       <c r="N63" s="21" t="inlineStr"/>
@@ -57969,13 +57969,13 @@
         <v>3912</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>4947</v>
+        <v>4950</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>6081</v>
+        <v>6078</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.407</v>
+        <v>0.4068</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>3.02</v>
@@ -57997,13 +57997,13 @@
         <v>10432</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>16529</v>
+        <v>16532</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>12879</v>
+        <v>12876</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.3233</v>
+        <v>0.3232</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>2.41</v>
@@ -58025,10 +58025,10 @@
         <v>20864</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>35269</v>
+        <v>35272</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>22551</v>
+        <v>22548</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>0.2866</v>
@@ -58053,10 +58053,10 @@
         <v>82152</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>168477</v>
+        <v>168480</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>53151</v>
+        <v>53148</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.175</v>
@@ -60909,13 +60909,13 @@
         <v>0.2618</v>
       </c>
       <c r="K63" s="22" t="n">
-        <v>4947</v>
+        <v>4950</v>
       </c>
       <c r="L63" s="22" t="n">
-        <v>6081</v>
+        <v>6078</v>
       </c>
       <c r="M63" s="23" t="n">
-        <v>0.407</v>
+        <v>0.4068</v>
       </c>
       <c r="N63" s="17" t="n">
         <v>3.02</v>
@@ -60927,7 +60927,7 @@
         <v>5000</v>
       </c>
       <c r="Q63" s="23" t="n">
-        <v>0.989</v>
+        <v>0.99</v>
       </c>
       <c r="R63" s="24" t="inlineStr"/>
     </row>
@@ -61069,22 +61069,22 @@
         <v>134196</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>275961</v>
+        <v>276192</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>410157</v>
+        <v>410388</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.8323</v>
+        <v>0.8328</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>82629</v>
+        <v>82398</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.1677</v>
+        <v>0.1672</v>
       </c>
       <c r="I7" s="9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="J7" s="9" t="n">
         <v>1.37</v>
@@ -61093,10 +61093,10 @@
         <v>17011</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>65618</v>
+        <v>65387</v>
       </c>
       <c r="M7" s="6" t="n">
-        <v>0.1332</v>
+        <v>0.1327</v>
       </c>
     </row>
     <row r="8">
@@ -61112,19 +61112,19 @@
         <v>543368</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>1023197</v>
+        <v>1023428</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>1566565</v>
+        <v>1566796</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.7924</v>
+        <v>0.7925</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>410521</v>
+        <v>410290</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>0.2076</v>
+        <v>0.2075</v>
       </c>
       <c r="I8" s="9" t="n">
         <v>1.93</v>
@@ -61136,10 +61136,10 @@
         <v>68249</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>342272</v>
+        <v>342041</v>
       </c>
       <c r="M8" s="6" t="n">
-        <v>0.1731</v>
+        <v>0.173</v>
       </c>
     </row>
     <row r="9">
@@ -61155,16 +61155,16 @@
         <v>1322318</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2549884</v>
+        <v>2550115</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>3872202</v>
+        <v>3872433</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>0.8078</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>921315</v>
+        <v>921084</v>
       </c>
       <c r="H9" s="6" t="n">
         <v>0.1922</v>
@@ -61179,10 +61179,10 @@
         <v>165472</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>755843</v>
+        <v>755612</v>
       </c>
       <c r="M9" s="6" t="n">
-        <v>0.1577</v>
+        <v>0.1576</v>
       </c>
     </row>
     <row r="10">
@@ -61198,16 +61198,16 @@
         <v>9577402</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>14555456</v>
+        <v>14555687</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>24132858</v>
+        <v>24133089</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.7423</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>8377316</v>
+        <v>8377085</v>
       </c>
       <c r="H10" s="6" t="n">
         <v>0.2577</v>
@@ -61222,7 +61222,7 @@
         <v>1122251</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>7255065</v>
+        <v>7254834</v>
       </c>
       <c r="M10" s="6" t="n">
         <v>0.2232</v>
@@ -61241,16 +61241,16 @@
         <v>4222865</v>
       </c>
       <c r="D11" s="5" t="n">
-        <v>7361015</v>
+        <v>7361246</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>11583880</v>
+        <v>11584111</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>0.784</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>3191345</v>
+        <v>3191114</v>
       </c>
       <c r="H11" s="6" t="n">
         <v>0.216</v>
@@ -61265,7 +61265,7 @@
         <v>510041</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>2681304</v>
+        <v>2681073</v>
       </c>
       <c r="M11" s="6" t="n">
         <v>0.1815</v>
@@ -61370,20 +61370,20 @@
         </is>
       </c>
       <c r="B18" s="5" t="n">
-        <v>275961</v>
+        <v>276192</v>
       </c>
       <c r="C18" s="5" t="inlineStr"/>
       <c r="D18" s="5" t="n">
-        <v>341066</v>
+        <v>341143</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>364269</v>
+        <v>364302</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>485182</v>
+        <v>485190</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>-0.2424</v>
+        <v>-0.2419</v>
       </c>
     </row>
     <row r="19">
@@ -61393,20 +61393,20 @@
         </is>
       </c>
       <c r="B19" s="5" t="n">
-        <v>82629</v>
+        <v>82398</v>
       </c>
       <c r="C19" s="5" t="inlineStr"/>
       <c r="D19" s="5" t="n">
-        <v>136840</v>
+        <v>136763</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>131616</v>
+        <v>131583</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>279244</v>
+        <v>279236</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>-0.3722</v>
+        <v>-0.3738</v>
       </c>
     </row>
     <row r="21">
@@ -64300,13 +64300,13 @@
         <v>15544</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>12377</v>
+        <v>12387</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>9678</v>
+        <v>9668</v>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.2574</v>
+        <v>0.2571</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>3.04</v>
@@ -64328,13 +64328,13 @@
         <v>48575</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>42020</v>
+        <v>42030</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>27680</v>
+        <v>27670</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.234</v>
+        <v>0.2339</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>2.81</v>
@@ -64356,10 +64356,10 @@
         <v>101036</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>98479</v>
+        <v>98489</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>46995</v>
+        <v>46985</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>0.1906</v>
@@ -64384,13 +64384,13 @@
         <v>186528</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>158539</v>
+        <v>158549</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>113591</v>
+        <v>113581</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>0.2477</v>
+        <v>0.2476</v>
       </c>
       <c r="G10" s="9" t="n">
         <v>2.89</v>
@@ -66792,13 +66792,13 @@
         <v>0.4134</v>
       </c>
       <c r="K63" s="22" t="n">
-        <v>12377</v>
+        <v>12387</v>
       </c>
       <c r="L63" s="22" t="n">
-        <v>9678</v>
+        <v>9668</v>
       </c>
       <c r="M63" s="23" t="n">
-        <v>0.2574</v>
+        <v>0.2571</v>
       </c>
       <c r="N63" s="16" t="n">
         <v>3.04</v>
@@ -66810,7 +66810,7 @@
         <v>15000</v>
       </c>
       <c r="Q63" s="23" t="n">
-        <v>0.825</v>
+        <v>0.826</v>
       </c>
       <c r="R63" s="24" t="inlineStr"/>
     </row>
@@ -69624,13 +69624,13 @@
         <v>3622</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>8567</v>
+        <v>8570</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>-229</v>
+        <v>-232</v>
       </c>
       <c r="F7" s="14" t="n">
-        <v>-0.0191</v>
+        <v>-0.0194</v>
       </c>
       <c r="G7" s="9" t="n">
         <v>1.4</v>
@@ -69652,13 +69652,13 @@
         <v>21732</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>29992</v>
+        <v>29995</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>17644</v>
+        <v>17641</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.2544</v>
+        <v>0.2543</v>
       </c>
       <c r="G8" s="9" t="n">
         <v>2.31</v>
@@ -69680,10 +69680,10 @@
         <v>56141</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>69199</v>
+        <v>69202</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>51369</v>
+        <v>51366</v>
       </c>
       <c r="F9" s="6" t="n">
         <v>0.2907</v>
@@ -69708,10 +69708,10 @@
         <v>103227</v>
       </c>
       <c r="D10" s="5" t="n">
-        <v>142877</v>
+        <v>142880</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>85693</v>
+        <v>85690</v>
       </c>
       <c r="F10" s="6" t="n">
         <v>0.2583</v>
@@ -72004,13 +72004,13 @@
         <v>0.3028</v>
       </c>
       <c r="K63" s="22" t="n">
-        <v>8567</v>
+        <v>8570</v>
       </c>
       <c r="L63" s="25" t="n">
-        <v>-229</v>
+        <v>-232</v>
       </c>
       <c r="M63" s="26" t="n">
-        <v>-0.0191</v>
+        <v>-0.0194</v>
       </c>
       <c r="N63" s="18" t="n">
         <v>1.4</v>
@@ -75605,13 +75605,13 @@
         </is>
       </c>
       <c r="C55" s="5" t="n">
-        <v>19128</v>
+        <v>19268</v>
       </c>
       <c r="D55" s="5" t="n">
         <v>23000</v>
       </c>
       <c r="E55" s="6" t="n">
-        <v>0.832</v>
+        <v>0.838</v>
       </c>
     </row>
   </sheetData>
@@ -76168,10 +76168,10 @@
         <v>233880</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>557627</v>
+        <v>557645</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>421995</v>
+        <v>421977</v>
       </c>
       <c r="G6" s="6" t="n">
         <v>0.3477</v>
@@ -76192,19 +76192,19 @@
         <v>129748</v>
       </c>
       <c r="M6" s="5" t="n">
-        <v>39016</v>
+        <v>38998</v>
       </c>
       <c r="N6" s="6" t="n">
-        <v>0.3007</v>
+        <v>0.3006</v>
       </c>
       <c r="O6" s="5" t="n">
-        <v>188585</v>
+        <v>188567</v>
       </c>
       <c r="P6" s="5" t="n">
-        <v>1939634</v>
+        <v>1939616</v>
       </c>
       <c r="Q6" s="5" t="n">
-        <v>1214047</v>
+        <v>1214029</v>
       </c>
       <c r="R6" s="4" t="n">
         <v>311</v>
@@ -76216,13 +76216,13 @@
         <v>1.11</v>
       </c>
       <c r="U6" s="5" t="n">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="V6" s="5" t="n">
         <v>3486</v>
       </c>
       <c r="W6" s="5" t="n">
-        <v>74000</v>
+        <v>80000</v>
       </c>
       <c r="X6" s="4" t="inlineStr">
         <is>
@@ -76328,10 +76328,10 @@
         <v>98175</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>243501</v>
+        <v>243502</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>21615</v>
+        <v>21614</v>
       </c>
       <c r="G8" s="6" t="n">
         <v>0.0595</v>
@@ -76352,19 +76352,19 @@
         <v>60507</v>
       </c>
       <c r="M8" s="5" t="n">
-        <v>14865</v>
+        <v>14864</v>
       </c>
       <c r="N8" s="6" t="n">
         <v>0.2457</v>
       </c>
       <c r="O8" s="5" t="n">
-        <v>14139</v>
+        <v>14138</v>
       </c>
       <c r="P8" s="5" t="n">
-        <v>1184772</v>
+        <v>1184771</v>
       </c>
       <c r="Q8" s="5" t="n">
-        <v>201098</v>
+        <v>201097</v>
       </c>
       <c r="R8" s="4" t="n">
         <v>75</v>
@@ -76408,10 +76408,10 @@
         <v>134304</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>138994</v>
+        <v>138996</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>61742</v>
+        <v>61740</v>
       </c>
       <c r="G9" s="6" t="n">
         <v>0.1843</v>
@@ -76432,19 +76432,19 @@
         <v>27920</v>
       </c>
       <c r="M9" s="5" t="n">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="N9" s="6" t="n">
-        <v>0.0049</v>
+        <v>0.0048</v>
       </c>
       <c r="O9" s="5" t="n">
-        <v>41996</v>
+        <v>41994</v>
       </c>
       <c r="P9" s="5" t="n">
-        <v>340570</v>
+        <v>340568</v>
       </c>
       <c r="Q9" s="5" t="n">
-        <v>206199</v>
+        <v>206197</v>
       </c>
       <c r="R9" s="4" t="n">
         <v>48</v>
@@ -76568,10 +76568,10 @@
         <v>86040</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>181159</v>
+        <v>181161</v>
       </c>
       <c r="F11" s="8" t="n">
-        <v>-20186</v>
+        <v>-20188</v>
       </c>
       <c r="G11" s="14" t="n">
         <v>-0.08169999999999999</v>
@@ -76592,19 +76592,19 @@
         <v>23880</v>
       </c>
       <c r="M11" s="8" t="n">
-        <v>-4126</v>
+        <v>-4128</v>
       </c>
       <c r="N11" s="14" t="n">
-        <v>-0.1728</v>
+        <v>-0.1729</v>
       </c>
       <c r="O11" s="8" t="n">
-        <v>-19483</v>
+        <v>-19485</v>
       </c>
       <c r="P11" s="5" t="n">
-        <v>450778</v>
+        <v>450776</v>
       </c>
       <c r="Q11" s="5" t="n">
-        <v>132861</v>
+        <v>132859</v>
       </c>
       <c r="R11" s="4" t="n">
         <v>60</v>
@@ -76648,10 +76648,10 @@
         <v>101036</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>98479</v>
+        <v>98489</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>46995</v>
+        <v>46985</v>
       </c>
       <c r="G12" s="6" t="n">
         <v>0.1906</v>
@@ -76672,19 +76672,19 @@
         <v>37599</v>
       </c>
       <c r="M12" s="5" t="n">
-        <v>9678</v>
+        <v>9668</v>
       </c>
       <c r="N12" s="6" t="n">
-        <v>0.2574</v>
+        <v>0.2571</v>
       </c>
       <c r="O12" s="5" t="n">
-        <v>27680</v>
+        <v>27670</v>
       </c>
       <c r="P12" s="5" t="n">
-        <v>113591</v>
+        <v>113581</v>
       </c>
       <c r="Q12" s="5" t="n">
-        <v>113591</v>
+        <v>113581</v>
       </c>
       <c r="R12" s="4" t="n">
         <v>52</v>
@@ -76728,13 +76728,13 @@
         <v>47329</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>115597</v>
+        <v>115624</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>39855</v>
+        <v>39828</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.1965</v>
+        <v>0.1964</v>
       </c>
       <c r="H13" s="4" t="n">
         <v>1.75</v>
@@ -76752,19 +76752,19 @@
         <v>26268</v>
       </c>
       <c r="M13" s="5" t="n">
-        <v>6550</v>
+        <v>6523</v>
       </c>
       <c r="N13" s="6" t="n">
-        <v>0.2494</v>
+        <v>0.2483</v>
       </c>
       <c r="O13" s="5" t="n">
-        <v>25520</v>
+        <v>25493</v>
       </c>
       <c r="P13" s="5" t="n">
-        <v>201309</v>
+        <v>201282</v>
       </c>
       <c r="Q13" s="5" t="n">
-        <v>97988</v>
+        <v>97961</v>
       </c>
       <c r="R13" s="4" t="n">
         <v>53</v>
@@ -76776,7 +76776,7 @@
         <v>1.23</v>
       </c>
       <c r="U13" s="5" t="n">
-        <v>2688</v>
+        <v>2689</v>
       </c>
       <c r="V13" s="5" t="n">
         <v>3615</v>
@@ -76808,13 +76808,13 @@
         <v>70930</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>88426</v>
+        <v>88432</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>35113</v>
+        <v>35107</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.1806</v>
+        <v>0.1805</v>
       </c>
       <c r="H14" s="4" t="n">
         <v>2.2</v>
@@ -76826,25 +76826,25 @@
         <v>3.51</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="L14" s="5" t="n">
         <v>14940</v>
       </c>
       <c r="M14" s="5" t="n">
-        <v>2262</v>
+        <v>2256</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>0.1514</v>
+        <v>0.151</v>
       </c>
       <c r="O14" s="5" t="n">
-        <v>26064</v>
+        <v>26058</v>
       </c>
       <c r="P14" s="5" t="n">
-        <v>1218114</v>
+        <v>1218108</v>
       </c>
       <c r="Q14" s="5" t="n">
-        <v>203297</v>
+        <v>203291</v>
       </c>
       <c r="R14" s="4" t="n">
         <v>41</v>
@@ -76856,7 +76856,7 @@
         <v>1.28</v>
       </c>
       <c r="U14" s="5" t="n">
-        <v>2763</v>
+        <v>2764</v>
       </c>
       <c r="V14" s="5" t="n">
         <v>3861</v>
@@ -76968,10 +76968,10 @@
         <v>56141</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>69199</v>
+        <v>69202</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>51369</v>
+        <v>51366</v>
       </c>
       <c r="G16" s="6" t="n">
         <v>0.2907</v>
@@ -76992,19 +76992,19 @@
         <v>11960</v>
       </c>
       <c r="M16" s="8" t="n">
-        <v>-229</v>
+        <v>-232</v>
       </c>
       <c r="N16" s="14" t="n">
-        <v>-0.0191</v>
+        <v>-0.0194</v>
       </c>
       <c r="O16" s="5" t="n">
-        <v>17644</v>
+        <v>17641</v>
       </c>
       <c r="P16" s="5" t="n">
-        <v>85693</v>
+        <v>85690</v>
       </c>
       <c r="Q16" s="5" t="n">
-        <v>85693</v>
+        <v>85690</v>
       </c>
       <c r="R16" s="4" t="n">
         <v>31</v>
@@ -77048,10 +77048,10 @@
         <v>45815</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>109421</v>
+        <v>109429</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>10598</v>
+        <v>10590</v>
       </c>
       <c r="G17" s="6" t="n">
         <v>0.0639</v>
@@ -77072,17 +77072,17 @@
         <v>0</v>
       </c>
       <c r="M17" s="8" t="n">
-        <v>-10474</v>
+        <v>-10482</v>
       </c>
       <c r="N17" s="6" t="inlineStr"/>
       <c r="O17" s="8" t="n">
-        <v>-13025</v>
+        <v>-13033</v>
       </c>
       <c r="P17" s="5" t="n">
-        <v>467314</v>
+        <v>467306</v>
       </c>
       <c r="Q17" s="5" t="n">
-        <v>111122</v>
+        <v>111114</v>
       </c>
       <c r="R17" s="4" t="n">
         <v>35</v>
@@ -77094,7 +77094,7 @@
         <v>1.35</v>
       </c>
       <c r="U17" s="5" t="n">
-        <v>4208</v>
+        <v>4209</v>
       </c>
       <c r="V17" s="5" t="n">
         <v>4616</v>
@@ -77286,13 +77286,13 @@
         <v>33264</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>69802</v>
+        <v>69813</v>
       </c>
       <c r="F20" s="8" t="n">
-        <v>-18406</v>
+        <v>-18417</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>-0.2174</v>
+        <v>-0.2175</v>
       </c>
       <c r="H20" s="4" t="n">
         <v>1.21</v>
@@ -77310,17 +77310,17 @@
         <v>0</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>-3359</v>
+        <v>-3370</v>
       </c>
       <c r="N20" s="6" t="inlineStr"/>
       <c r="O20" s="8" t="n">
-        <v>-10899</v>
+        <v>-10910</v>
       </c>
       <c r="P20" s="5" t="n">
-        <v>360933</v>
+        <v>360922</v>
       </c>
       <c r="Q20" s="5" t="n">
-        <v>82057</v>
+        <v>82046</v>
       </c>
       <c r="R20" s="4" t="n">
         <v>18</v>
@@ -77332,7 +77332,7 @@
         <v>1.38</v>
       </c>
       <c r="U20" s="5" t="n">
-        <v>5369</v>
+        <v>5370</v>
       </c>
       <c r="V20" s="5" t="n">
         <v>3954</v>
@@ -77366,10 +77366,10 @@
         <v>20864</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>35269</v>
+        <v>35272</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>22551</v>
+        <v>22548</v>
       </c>
       <c r="G21" s="6" t="n">
         <v>0.2866</v>
@@ -77390,19 +77390,19 @@
         <v>14940</v>
       </c>
       <c r="M21" s="5" t="n">
-        <v>6081</v>
+        <v>6078</v>
       </c>
       <c r="N21" s="6" t="n">
-        <v>0.407</v>
+        <v>0.4068</v>
       </c>
       <c r="O21" s="5" t="n">
-        <v>12879</v>
+        <v>12876</v>
       </c>
       <c r="P21" s="5" t="n">
-        <v>53151</v>
+        <v>53148</v>
       </c>
       <c r="Q21" s="5" t="n">
-        <v>35038</v>
+        <v>35035</v>
       </c>
       <c r="R21" s="4" t="n">
         <v>16</v>
@@ -78344,7 +78344,7 @@
         </is>
       </c>
       <c r="E33" s="5" t="n">
-        <v>159020</v>
+        <v>159160</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
@@ -78557,7 +78557,7 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>74000</v>
+        <v>80000</v>
       </c>
       <c r="D6" s="6" t="n">
         <v>0.996</v>
@@ -78575,13 +78575,13 @@
         <v>0.23</v>
       </c>
       <c r="I6" s="8" t="n">
-        <v>-29751</v>
+        <v>-32158</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>29751</v>
+        <v>32158</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>421995</v>
+        <v>421977</v>
       </c>
     </row>
     <row r="7">
@@ -78659,7 +78659,7 @@
         <v>-14569</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>21615</v>
+        <v>21614</v>
       </c>
     </row>
     <row r="9">
@@ -78737,7 +78737,7 @@
         <v>-11411</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>-20186</v>
+        <v>-20188</v>
       </c>
     </row>
     <row r="11">
@@ -78770,13 +78770,13 @@
         <v>-0.232</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>4064</v>
+        <v>4065</v>
       </c>
       <c r="J11" s="8" t="n">
-        <v>-4064</v>
+        <v>-4065</v>
       </c>
       <c r="K11" s="5" t="n">
-        <v>10598</v>
+        <v>10590</v>
       </c>
     </row>
     <row r="12">
@@ -78809,13 +78809,13 @@
         <v>0.22</v>
       </c>
       <c r="I12" s="8" t="n">
-        <v>-3844</v>
+        <v>-3843</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>3844</v>
+        <v>3843</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>51369</v>
+        <v>51366</v>
       </c>
     </row>
     <row r="13">
@@ -78887,13 +78887,13 @@
         <v>-0.059</v>
       </c>
       <c r="I14" s="5" t="n">
-        <v>1694</v>
+        <v>1700</v>
       </c>
       <c r="J14" s="8" t="n">
-        <v>-1694</v>
+        <v>-1700</v>
       </c>
       <c r="K14" s="5" t="n">
-        <v>39855</v>
+        <v>39828</v>
       </c>
     </row>
     <row r="15">
@@ -78923,16 +78923,16 @@
         <v>0.87</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>0.148</v>
+        <v>0.147</v>
       </c>
       <c r="I15" s="8" t="n">
-        <v>-1291</v>
+        <v>-1290</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>1291</v>
+        <v>1290</v>
       </c>
       <c r="K15" s="5" t="n">
-        <v>22551</v>
+        <v>22548</v>
       </c>
     </row>
     <row r="16">
@@ -78965,13 +78965,13 @@
         <v>0.034</v>
       </c>
       <c r="I16" s="8" t="n">
-        <v>-894</v>
+        <v>-891</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>46995</v>
+        <v>46985</v>
       </c>
     </row>
     <row r="17">
@@ -79049,7 +79049,7 @@
         <v>383</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>61742</v>
+        <v>61740</v>
       </c>
     </row>
     <row r="19">
@@ -79076,19 +79076,19 @@
         <v>1.57</v>
       </c>
       <c r="G19" s="4" t="n">
-        <v>0.63</v>
+        <v>0.62</v>
       </c>
       <c r="H19" s="7" t="n">
         <v>-0.022</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="J19" s="8" t="n">
-        <v>-341</v>
+        <v>-342</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>35113</v>
+        <v>35107</v>
       </c>
     </row>
   </sheetData>
@@ -80885,19 +80885,19 @@
         <v>134213</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>275961</v>
+        <v>276192</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>82612</v>
+        <v>82381</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.1676</v>
+        <v>0.1672</v>
       </c>
       <c r="H40" s="9" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="I40" s="5" t="n">
-        <v>136883</v>
+        <v>136806</v>
       </c>
       <c r="J40" s="4" t="inlineStr"/>
     </row>
